--- a/coretp/plans/svadu/SVADU_TP.xlsx
+++ b/coretp/plans/svadu/SVADU_TP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Documents/Clean Test Plans/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF0A1B10-0A63-8246-B6F9-1063E124E1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE89A2E-FEAA-F34D-A0C8-FA3DA1E8D9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-13720" windowWidth="51200" windowHeight="27200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="svadu-TP" sheetId="12" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>Scenario details</t>
   </si>
@@ -54,49 +54,11 @@
   </si>
   <si>
     <t>Pseudo Ops V2</t>
-  </si>
-  <si>
-    <t>Faults on SVADU disabled</t>
   </si>
   <si>
     <t>When svadu disabled i.e menvcfg.adue=0 , 
 1. All memory access should fault when pte.a=0
 2. Store/Amo/sc/zicboz should fault when pte.d=0</t>
-  </si>
-  <si>
-    <t>Priv_mode = any with eff_priv mode=S/U
-paging_mode = {SV57,SV48,SV39}
-instr_a = {load,fetch,lr,zicbom}
-instr_b = {store,amo,sc,zicboz}
-ptw pa mem_type = {any}
-pte.ad = {00,01,10}
-load = {normal, compressed, FP}
-store = {normal, compressed, FP}</t>
-  </si>
-  <si>
-    <t>SVADU enabled : Hardware update of access/dirty bits (pte mem_type=cacheable memory)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When svadu enabled i.e menvcfg.adue=1 , pte pa mem_type = cacheable
-1. all memory access should update pte.a bit if pte.a=0
-2. Store/Amo/sc/zicboz should update  pte.d bit if pte.d=0
-Access/Dirty  bit update:
-1. Make Pte.AD = 00/10/10
-2. Sfence.vma followed by rand instructions
-3. Load from pte (may or may not have pte.A=1)
-4. any access to hardware update A/D bits  without fault
-6. Load from pte to see pte.ad bits update based on access type
-</t>
-  </si>
-  <si>
-    <t>Priv_mode = any with eff_priv mode=S/U
-paging_mode = {SV57,SV48,SV39}
-instr_a = {load,fetch,lr,zicbom}
-instr_b = {store,amo,sc,zicboz}
-ptw pa mem_type = {cacheable}
-pte.ad = {00,01,10}
-load = {normal, compressed, FP}
-store = {normal, compressed, FP}</t>
   </si>
   <si>
     <t>SID_SVADU_01_fault_on_a_bit_cleared</t>
@@ -149,17 +111,86 @@
 Store(memory=mem, value=store_val)
 AssertException(cause=STORE_AMO_PAGE_FAULT, code=[store_op])</t>
   </si>
+  <si>
+    <t>Normative Rule Mapping</t>
+  </si>
+  <si>
+    <t>Svadu_hw_update_a_d_bits</t>
+  </si>
+  <si>
+    <t>MENVCFG.adue is writable. When disabled, fall back to SVADE</t>
+  </si>
+  <si>
+    <t>SVADU enabled : Hardware update of access bits (pte mem_type=cacheable memory)</t>
+  </si>
+  <si>
+    <t>SVADU enabled : Hardware update of dirty bits (pte mem_type=cacheable memory)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When svadu enabled, all store access should update pte.d bit if pte.d=0
+Access bit update:
+1. Reserve a region and make leaf pte.AD = {00, 10}
+2. Perform sfence.vma to expose to main code
+3. Perform a store on the region from step 1
+4. Load leaf pte entry from reserved region to see pte.d bit update
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When svadu enabled, all memory access should update pte.a bit if pte.a=0
+Access bit update:
+1. Reserve a region and make leaf pte.AD = {00, 01}
+2. Perform sfence.vma to expose to main code
+3. Perform a load on the region from step 1
+4. Load leaf pte entry from reserved region to see pte.a bit update
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test privilege mode=S/U
+paging_mode = {SV57,SV48,SV39}
+pte.ad = {00,01,10}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test privilege mode=S/U
+paging_mode = {SV57,SV48,SV39}
+pte.ad = {00,01}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test privilege mode=S/U
+paging_mode = {SV57,SV48,SV39}
+pte.ad = {00,10}
+</t>
+  </si>
+  <si>
+    <t>Svadu_hypervisor_adue_writable
+Svadu_disabled_hw_update_falls_back_to_svade</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,42 +297,48 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6B2351-8E81-490A-A1F4-0DA5C6821380}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -585,19 +622,20 @@
     <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="48.6640625" customWidth="1"/>
     <col min="5" max="5" width="90.6640625" customWidth="1"/>
-    <col min="6" max="6" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="11"/>
     </row>
-    <row r="2" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -613,78 +651,93 @@
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="128" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:6" ht="128" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="130" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="232" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="229" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="130" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="232" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="229" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="F6" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="E1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
